--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321294</v>
+        <v>123321313</v>
       </c>
       <c r="B2" t="n">
-        <v>98282</v>
+        <v>98402</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597883</v>
+        <v>597970</v>
       </c>
       <c r="R2" t="n">
-        <v>6818860</v>
+        <v>6818756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321318</v>
+        <v>123321294</v>
       </c>
       <c r="B3" t="n">
-        <v>58338</v>
+        <v>98285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,31 +826,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598048</v>
+        <v>597883</v>
       </c>
       <c r="R3" t="n">
-        <v>6818708</v>
+        <v>6818860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321320</v>
+        <v>123321304</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,30 +957,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598002</v>
+        <v>597914</v>
       </c>
       <c r="R4" t="n">
-        <v>6818687</v>
+        <v>6818765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321306</v>
+        <v>123321315</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,30 +1092,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597934</v>
+        <v>598006</v>
       </c>
       <c r="R5" t="n">
-        <v>6818761</v>
+        <v>6818738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321304</v>
+        <v>123321316</v>
       </c>
       <c r="B6" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597914</v>
+        <v>598013</v>
       </c>
       <c r="R6" t="n">
-        <v>6818765</v>
+        <v>6818734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321313</v>
+        <v>123321306</v>
       </c>
       <c r="B7" t="n">
-        <v>98399</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,30 +1362,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597970</v>
+        <v>597934</v>
       </c>
       <c r="R7" t="n">
-        <v>6818756</v>
+        <v>6818761</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321316</v>
+        <v>123321318</v>
       </c>
       <c r="B8" t="n">
-        <v>98282</v>
+        <v>58341</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,31 +1501,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598013</v>
+        <v>598048</v>
       </c>
       <c r="R8" t="n">
-        <v>6818734</v>
+        <v>6818708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321315</v>
+        <v>123321320</v>
       </c>
       <c r="B9" t="n">
-        <v>98386</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,25 +1632,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598006</v>
+        <v>598002</v>
       </c>
       <c r="R9" t="n">
-        <v>6818738</v>
+        <v>6818687</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1748,6 +1748,156 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123434953</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90957</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gillermyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>597900</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6818723</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2024_684</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I granskog</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marcus Lewin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321313</v>
+        <v>123321316</v>
       </c>
       <c r="B2" t="n">
-        <v>98402</v>
+        <v>98287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597970</v>
+        <v>598013</v>
       </c>
       <c r="R2" t="n">
-        <v>6818756</v>
+        <v>6818734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321294</v>
+        <v>123321315</v>
       </c>
       <c r="B3" t="n">
-        <v>98285</v>
+        <v>98391</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597883</v>
+        <v>598006</v>
       </c>
       <c r="R3" t="n">
-        <v>6818860</v>
+        <v>6818738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321304</v>
+        <v>123321294</v>
       </c>
       <c r="B4" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597914</v>
+        <v>597883</v>
       </c>
       <c r="R4" t="n">
-        <v>6818765</v>
+        <v>6818860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321315</v>
+        <v>123321313</v>
       </c>
       <c r="B5" t="n">
-        <v>98389</v>
+        <v>98404</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,16 +1096,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598006</v>
+        <v>597970</v>
       </c>
       <c r="R5" t="n">
-        <v>6818738</v>
+        <v>6818756</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321316</v>
+        <v>123321306</v>
       </c>
       <c r="B6" t="n">
-        <v>98285</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,30 +1227,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598013</v>
+        <v>597934</v>
       </c>
       <c r="R6" t="n">
-        <v>6818734</v>
+        <v>6818761</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321306</v>
+        <v>123321318</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>58341</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,35 +1362,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597934</v>
+        <v>598048</v>
       </c>
       <c r="R7" t="n">
-        <v>6818761</v>
+        <v>6818708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321318</v>
+        <v>123321304</v>
       </c>
       <c r="B8" t="n">
-        <v>58341</v>
+        <v>98287</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,31 +1501,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598048</v>
+        <v>597914</v>
       </c>
       <c r="R8" t="n">
-        <v>6818708</v>
+        <v>6818765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1623,7 +1623,7 @@
         <v>123321320</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321316</v>
+        <v>123321306</v>
       </c>
       <c r="B2" t="n">
-        <v>98287</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598013</v>
+        <v>597934</v>
       </c>
       <c r="R2" t="n">
-        <v>6818734</v>
+        <v>6818761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321315</v>
+        <v>123321320</v>
       </c>
       <c r="B3" t="n">
-        <v>98391</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598006</v>
+        <v>598002</v>
       </c>
       <c r="R3" t="n">
-        <v>6818738</v>
+        <v>6818687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321294</v>
+        <v>123321318</v>
       </c>
       <c r="B4" t="n">
-        <v>98287</v>
+        <v>58341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597883</v>
+        <v>598048</v>
       </c>
       <c r="R4" t="n">
-        <v>6818860</v>
+        <v>6818708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321313</v>
+        <v>123321315</v>
       </c>
       <c r="B5" t="n">
-        <v>98404</v>
+        <v>98397</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,16 +1096,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597970</v>
+        <v>598006</v>
       </c>
       <c r="R5" t="n">
-        <v>6818756</v>
+        <v>6818738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321306</v>
+        <v>123321294</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,30 +1227,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597934</v>
+        <v>597883</v>
       </c>
       <c r="R6" t="n">
-        <v>6818761</v>
+        <v>6818860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321318</v>
+        <v>123321316</v>
       </c>
       <c r="B7" t="n">
-        <v>58341</v>
+        <v>98293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,31 +1366,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598048</v>
+        <v>598013</v>
       </c>
       <c r="R7" t="n">
-        <v>6818708</v>
+        <v>6818734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321304</v>
+        <v>123321313</v>
       </c>
       <c r="B8" t="n">
-        <v>98287</v>
+        <v>98410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597914</v>
+        <v>597970</v>
       </c>
       <c r="R8" t="n">
-        <v>6818765</v>
+        <v>6818756</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321320</v>
+        <v>123321304</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,30 +1632,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598002</v>
+        <v>597914</v>
       </c>
       <c r="R9" t="n">
-        <v>6818687</v>
+        <v>6818765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,7 +1758,7 @@
         <v>123434953</v>
       </c>
       <c r="B10" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321304</v>
+        <v>123321320</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597914</v>
+        <v>598002</v>
       </c>
       <c r="R2" t="n">
-        <v>6818765</v>
+        <v>6818687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321316</v>
+        <v>123321313</v>
       </c>
       <c r="B3" t="n">
-        <v>98296</v>
+        <v>98430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598013</v>
+        <v>597970</v>
       </c>
       <c r="R3" t="n">
-        <v>6818734</v>
+        <v>6818756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321315</v>
+        <v>123321306</v>
       </c>
       <c r="B4" t="n">
-        <v>98400</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,30 +957,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598006</v>
+        <v>597934</v>
       </c>
       <c r="R4" t="n">
-        <v>6818738</v>
+        <v>6818761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,7 +1083,7 @@
         <v>123321318</v>
       </c>
       <c r="B5" t="n">
-        <v>58341</v>
+        <v>58347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321320</v>
+        <v>123321304</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98313</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,30 +1227,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598002</v>
+        <v>597914</v>
       </c>
       <c r="R6" t="n">
-        <v>6818687</v>
+        <v>6818765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321294</v>
+        <v>123321315</v>
       </c>
       <c r="B7" t="n">
-        <v>98296</v>
+        <v>98417</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,26 +1366,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597883</v>
+        <v>598006</v>
       </c>
       <c r="R7" t="n">
-        <v>6818860</v>
+        <v>6818738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321306</v>
+        <v>123321294</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98313</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,30 +1497,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597934</v>
+        <v>597883</v>
       </c>
       <c r="R8" t="n">
-        <v>6818761</v>
+        <v>6818860</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321313</v>
+        <v>123321316</v>
       </c>
       <c r="B9" t="n">
-        <v>98413</v>
+        <v>98313</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,26 +1636,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597970</v>
+        <v>598013</v>
       </c>
       <c r="R9" t="n">
-        <v>6818756</v>
+        <v>6818734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,7 +1758,7 @@
         <v>123434953</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321320</v>
+        <v>123321294</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598002</v>
+        <v>597883</v>
       </c>
       <c r="R2" t="n">
-        <v>6818687</v>
+        <v>6818860</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321313</v>
+        <v>123321304</v>
       </c>
       <c r="B3" t="n">
-        <v>98430</v>
+        <v>98419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597970</v>
+        <v>597914</v>
       </c>
       <c r="R3" t="n">
-        <v>6818756</v>
+        <v>6818765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321306</v>
+        <v>123321318</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>58350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597934</v>
+        <v>598048</v>
       </c>
       <c r="R4" t="n">
-        <v>6818761</v>
+        <v>6818708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321318</v>
+        <v>123321316</v>
       </c>
       <c r="B5" t="n">
-        <v>58347</v>
+        <v>98419</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,31 +1096,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598048</v>
+        <v>598013</v>
       </c>
       <c r="R5" t="n">
-        <v>6818708</v>
+        <v>6818734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321304</v>
+        <v>123321306</v>
       </c>
       <c r="B6" t="n">
-        <v>98313</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,30 +1227,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597914</v>
+        <v>597934</v>
       </c>
       <c r="R6" t="n">
-        <v>6818765</v>
+        <v>6818761</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321315</v>
+        <v>123321320</v>
       </c>
       <c r="B7" t="n">
-        <v>98417</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,25 +1362,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598006</v>
+        <v>598002</v>
       </c>
       <c r="R7" t="n">
-        <v>6818738</v>
+        <v>6818687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321294</v>
+        <v>123321315</v>
       </c>
       <c r="B8" t="n">
-        <v>98313</v>
+        <v>98523</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597883</v>
+        <v>598006</v>
       </c>
       <c r="R8" t="n">
-        <v>6818860</v>
+        <v>6818738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321316</v>
+        <v>123321313</v>
       </c>
       <c r="B9" t="n">
-        <v>98313</v>
+        <v>98536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,26 +1636,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598013</v>
+        <v>597970</v>
       </c>
       <c r="R9" t="n">
-        <v>6818734</v>
+        <v>6818756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,7 +1758,7 @@
         <v>123434953</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321294</v>
+        <v>123321316</v>
       </c>
       <c r="B2" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597883</v>
+        <v>598013</v>
       </c>
       <c r="R2" t="n">
-        <v>6818860</v>
+        <v>6818734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321304</v>
+        <v>123321306</v>
       </c>
       <c r="B3" t="n">
-        <v>98419</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,30 +822,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597914</v>
+        <v>597934</v>
       </c>
       <c r="R3" t="n">
-        <v>6818765</v>
+        <v>6818761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321318</v>
+        <v>123321304</v>
       </c>
       <c r="B4" t="n">
-        <v>58350</v>
+        <v>98421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598048</v>
+        <v>597914</v>
       </c>
       <c r="R4" t="n">
-        <v>6818708</v>
+        <v>6818765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321316</v>
+        <v>123321318</v>
       </c>
       <c r="B5" t="n">
-        <v>98419</v>
+        <v>58351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,31 +1096,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598013</v>
+        <v>598048</v>
       </c>
       <c r="R5" t="n">
-        <v>6818734</v>
+        <v>6818708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321306</v>
+        <v>123321320</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597934</v>
+        <v>598002</v>
       </c>
       <c r="R6" t="n">
-        <v>6818761</v>
+        <v>6818687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321320</v>
+        <v>123321315</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,25 +1362,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598002</v>
+        <v>598006</v>
       </c>
       <c r="R7" t="n">
-        <v>6818687</v>
+        <v>6818738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321315</v>
+        <v>123321313</v>
       </c>
       <c r="B8" t="n">
-        <v>98523</v>
+        <v>98538</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598006</v>
+        <v>597970</v>
       </c>
       <c r="R8" t="n">
-        <v>6818738</v>
+        <v>6818756</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321313</v>
+        <v>123321294</v>
       </c>
       <c r="B9" t="n">
-        <v>98536</v>
+        <v>98421</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,26 +1636,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597970</v>
+        <v>597883</v>
       </c>
       <c r="R9" t="n">
-        <v>6818756</v>
+        <v>6818860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1758,7 +1758,7 @@
         <v>123434953</v>
       </c>
       <c r="B10" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321316</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321306</v>
+        <v>123321294</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>97996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,30 +822,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597934</v>
+        <v>597883</v>
       </c>
       <c r="R3" t="n">
-        <v>6818761</v>
+        <v>6818860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321304</v>
+        <v>123321315</v>
       </c>
       <c r="B4" t="n">
-        <v>98421</v>
+        <v>98100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,26 +961,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597914</v>
+        <v>598006</v>
       </c>
       <c r="R4" t="n">
-        <v>6818765</v>
+        <v>6818738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321318</v>
+        <v>123321304</v>
       </c>
       <c r="B5" t="n">
-        <v>58351</v>
+        <v>97996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,31 +1096,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598048</v>
+        <v>597914</v>
       </c>
       <c r="R5" t="n">
-        <v>6818708</v>
+        <v>6818765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321320</v>
+        <v>123321306</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598002</v>
+        <v>597934</v>
       </c>
       <c r="R6" t="n">
-        <v>6818687</v>
+        <v>6818761</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321315</v>
+        <v>123321320</v>
       </c>
       <c r="B7" t="n">
-        <v>98525</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,25 +1362,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598006</v>
+        <v>598002</v>
       </c>
       <c r="R7" t="n">
-        <v>6818738</v>
+        <v>6818687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1488,7 +1488,7 @@
         <v>123321313</v>
       </c>
       <c r="B8" t="n">
-        <v>98538</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321294</v>
+        <v>123321318</v>
       </c>
       <c r="B9" t="n">
-        <v>98421</v>
+        <v>58351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597883</v>
+        <v>598048</v>
       </c>
       <c r="R9" t="n">
-        <v>6818860</v>
+        <v>6818708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321316</v>
+        <v>123321304</v>
       </c>
       <c r="B2" t="n">
         <v>97996</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598013</v>
+        <v>597914</v>
       </c>
       <c r="R2" t="n">
-        <v>6818734</v>
+        <v>6818765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321294</v>
+        <v>123321318</v>
       </c>
       <c r="B3" t="n">
-        <v>97996</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,31 +826,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597883</v>
+        <v>598048</v>
       </c>
       <c r="R3" t="n">
-        <v>6818860</v>
+        <v>6818708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321315</v>
+        <v>123321313</v>
       </c>
       <c r="B4" t="n">
-        <v>98100</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598006</v>
+        <v>597970</v>
       </c>
       <c r="R4" t="n">
-        <v>6818738</v>
+        <v>6818756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,7 +1080,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321304</v>
+        <v>123321294</v>
       </c>
       <c r="B5" t="n">
         <v>97996</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597914</v>
+        <v>597883</v>
       </c>
       <c r="R5" t="n">
-        <v>6818765</v>
+        <v>6818860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321320</v>
+        <v>123321315</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>98100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,25 +1362,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598002</v>
+        <v>598006</v>
       </c>
       <c r="R7" t="n">
-        <v>6818687</v>
+        <v>6818738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321313</v>
+        <v>123321316</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>97996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597970</v>
+        <v>598013</v>
       </c>
       <c r="R8" t="n">
-        <v>6818756</v>
+        <v>6818734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321318</v>
+        <v>123321320</v>
       </c>
       <c r="B9" t="n">
-        <v>58351</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,35 +1632,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598048</v>
+        <v>598002</v>
       </c>
       <c r="R9" t="n">
-        <v>6818708</v>
+        <v>6818687</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321304</v>
+        <v>123321294</v>
       </c>
       <c r="B2" t="n">
         <v>97996</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597914</v>
+        <v>597883</v>
       </c>
       <c r="R2" t="n">
-        <v>6818765</v>
+        <v>6818860</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_680</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Marcus Lewin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321313</v>
+        <v>123321315</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597970</v>
+        <v>598006</v>
       </c>
       <c r="R4" t="n">
-        <v>6818756</v>
+        <v>6818738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,7 +1080,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321294</v>
+        <v>123321304</v>
       </c>
       <c r="B5" t="n">
         <v>97996</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597883</v>
+        <v>597914</v>
       </c>
       <c r="R5" t="n">
-        <v>6818860</v>
+        <v>6818765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_680</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marcus Lewin</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321306</v>
+        <v>123321313</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,30 +1227,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597934</v>
+        <v>597970</v>
       </c>
       <c r="R6" t="n">
-        <v>6818761</v>
+        <v>6818756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321315</v>
+        <v>123321316</v>
       </c>
       <c r="B7" t="n">
-        <v>98100</v>
+        <v>97996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,26 +1366,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598006</v>
+        <v>598013</v>
       </c>
       <c r="R7" t="n">
-        <v>6818738</v>
+        <v>6818734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321316</v>
+        <v>123321306</v>
       </c>
       <c r="B8" t="n">
-        <v>97996</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,30 +1497,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598013</v>
+        <v>597934</v>
       </c>
       <c r="R8" t="n">
-        <v>6818734</v>
+        <v>6818761</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14648-2024 artfynd.xlsx
+++ b/artfynd/A 14648-2024 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321318</v>
+        <v>123321313</v>
       </c>
       <c r="B3" t="n">
-        <v>58351</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,31 +826,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598048</v>
+        <v>597970</v>
       </c>
       <c r="R3" t="n">
-        <v>6818708</v>
+        <v>6818756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_657</t>
+          <t>2024_662</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i bäck</t>
+          <t>påtaglig förekomst  vid bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321315</v>
+        <v>123321306</v>
       </c>
       <c r="B4" t="n">
-        <v>98100</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,30 +957,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598006</v>
+        <v>597934</v>
       </c>
       <c r="R4" t="n">
-        <v>6818738</v>
+        <v>6818761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_660</t>
+          <t>2024_668</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>mycket riklig förekomst vid och längsmed bäck</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321304</v>
+        <v>123321320</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,30 +1092,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597914</v>
+        <v>598002</v>
       </c>
       <c r="R5" t="n">
-        <v>6818765</v>
+        <v>6818687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_670</t>
+          <t>2024_654</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sparsam förekomst</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123321313</v>
+        <v>123321316</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>97996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597970</v>
+        <v>598013</v>
       </c>
       <c r="R6" t="n">
-        <v>6818756</v>
+        <v>6818734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_662</t>
+          <t>2024_659</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>påtaglig förekomst  vid bäck</t>
+          <t>vid bäck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123321316</v>
+        <v>123321318</v>
       </c>
       <c r="B7" t="n">
-        <v>97996</v>
+        <v>58351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,31 +1366,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598013</v>
+        <v>598048</v>
       </c>
       <c r="R7" t="n">
-        <v>6818734</v>
+        <v>6818708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_659</t>
+          <t>2024_657</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>vid bäck</t>
+          <t>i bäck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321306</v>
+        <v>123321315</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>98100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,30 +1497,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597934</v>
+        <v>598006</v>
       </c>
       <c r="R8" t="n">
-        <v>6818761</v>
+        <v>6818738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_668</t>
+          <t>2024_660</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>mycket riklig förekomst vid och längsmed bäck</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321320</v>
+        <v>123321304</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>97996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,30 +1632,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598002</v>
+        <v>597914</v>
       </c>
       <c r="R9" t="n">
-        <v>6818687</v>
+        <v>6818765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_654</t>
+          <t>2024_670</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>sparsam förekomst</t>
         </is>
       </c>
       <c r="AD9" t="b">
